--- a/data/target_form/영광군농협.xlsx
+++ b/data/target_form/영광군농협.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae7f7f815e37025b/문서/365건강농산/목표양식/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skawl\PycharmProjects\365배포\data\target_form\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{E26B2D6D-0915-47F2-9AB3-7D2BE14664FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20F76731-D791-4BD3-AEAE-4C1714CFC5C3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF8F90B-86CA-4EAB-B4D6-D4C72B711BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="16090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
     <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1'!$A$2:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1'!$A$1:$Q$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>수량</t>
   </si>
@@ -74,18 +74,6 @@
   </si>
   <si>
     <t>택배사코드(필수)</t>
-  </si>
-  <si>
-    <t>발신: 365건강농산</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>발신:365건강농산</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>수  신 :  영 광 군 농 협</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>번호</t>
@@ -121,7 +109,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -148,28 +136,7 @@
       <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <sz val="22"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -205,7 +172,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -241,15 +208,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -259,54 +217,42 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -324,10 +270,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -620,152 +562,127 @@
   <sheetPr codeName="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.08203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="53.58203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.08203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.9140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="18.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.08203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="53.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.08203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.9140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="18.5" style="3" bestFit="1" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B1" s="14" t="s">
+    <row r="1" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="10">
+        <v>1</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="11">
+        <v>2148773112</v>
+      </c>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="2"/>
-      <c r="N1" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-    </row>
-    <row r="2" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="11">
-        <v>1</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="12">
-        <v>2148773112</v>
-      </c>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q3" s="11"/>
+      <c r="Q2" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q2" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:Q14">
-      <sortCondition ref="C2"/>
+  <autoFilter ref="A1:Q1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q13">
+      <sortCondition ref="C1"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="2">
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="B1:H1"/>
-  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
